--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12118</v>
+        <v>12273</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15465</v>
+        <v>15642</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3347</v>
+        <v>-3369</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7251</v>
+        <v>7361</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10835</v>
+        <v>11565</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3584</v>
+        <v>-4204</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -614,51 +605,6 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>20-SEP-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-445</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7140</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>13387</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-6247</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12273</v>
+        <v>10964</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15642</v>
+        <v>17728</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3369</v>
+        <v>-6764</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7361</v>
+        <v>11485</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11565</v>
+        <v>17728</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4204</v>
+        <v>-6243</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -599,12 +608,147 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>14-JUN-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-445</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>7694</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>11555</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>21-JUN-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-445</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7215</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10358</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-3143</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-445</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>13528</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-6200</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -639,10 +639,10 @@
         <v>7694</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11555</v>
+        <v>12331</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3861</v>
+        <v>-4637</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7215</v>
+        <v>7328</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10358</v>
+        <v>13528</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3143</v>
+        <v>-6200</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,57 +698,12 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-445</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>7328</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>13528</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-6200</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10964</v>
+        <v>9703</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17728</v>
+        <v>13514</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6764</v>
+        <v>-3811</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11485</v>
+        <v>9703</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17728</v>
+        <v>15608</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6243</v>
+        <v>-5905</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7694</v>
+        <v>8362</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>12331</v>
+        <v>13514</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4637</v>
+        <v>-5152</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7328</v>
+        <v>7301</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13528</v>
+        <v>10931</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6200</v>
+        <v>-3630</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,12 +698,57 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-445</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-143</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7664</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>13514</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-5850</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_AHB_threats.xlsx
+++ b/excel_routes/route_HMB_AHB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9703</v>
+        <v>9591</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13514</v>
+        <v>15483</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3811</v>
+        <v>-5892</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9703</v>
+        <v>8266</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15608</v>
+        <v>12199</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5905</v>
+        <v>-3933</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,145 +610,10 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-445</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8362</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>13514</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-5152</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>21-JUN-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-445</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>7301</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>10931</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-3630</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-445</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>7664</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>13514</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-5850</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
